--- a/evaluation_multimodels/runs/2026-09-21-minimal32-five-self-included/pairs/kimi_kimi-k2.6_judge_high__vs__kimi_kimi-k2.6_judge_high.xlsx
+++ b/evaluation_multimodels/runs/2026-09-21-minimal32-five-self-included/pairs/kimi_kimi-k2.6_judge_high__vs__kimi_kimi-k2.6_judge_high.xlsx
@@ -2038,33 +2038,35 @@
       <c r="H2" t="b">
         <v>1</v>
       </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>11894.59045801777</v>
+        <v>14216.35495900409</v>
       </c>
       <c r="M2" t="n">
-        <v>0.008124974556267262</v>
+        <v>2630.244250001851</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2103,33 +2105,35 @@
       <c r="H3" t="b">
         <v>1</v>
       </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>65250.09058299474</v>
+        <v>13487.6657500281</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05062500713393092</v>
+        <v>1248.360458004754</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2168,33 +2172,35 @@
       <c r="H4" t="b">
         <v>1</v>
       </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>0.006166985258460045</v>
+        <v>11183.97691700375</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01699995482340455</v>
+        <v>1610.10399996303</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2233,33 +2239,35 @@
       <c r="H5" t="b">
         <v>1</v>
       </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>0.01816701842471957</v>
+        <v>8046.871040947735</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02616696292534471</v>
+        <v>1171.825124998577</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2298,33 +2306,35 @@
       <c r="H6" t="b">
         <v>1</v>
       </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>68931.19487504009</v>
+        <v>13961.15879202262</v>
       </c>
       <c r="M6" t="n">
-        <v>0.009874987881630659</v>
+        <v>1195.20554097835</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2363,33 +2373,35 @@
       <c r="H7" t="b">
         <v>1</v>
       </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>0.006582995411008596</v>
+        <v>10047.84108296735</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01633301144465804</v>
+        <v>1738.227292022202</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2428,33 +2440,35 @@
       <c r="H8" t="b">
         <v>1</v>
       </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>0.004250032361596823</v>
+        <v>3222.872207988985</v>
       </c>
       <c r="M8" t="n">
-        <v>0.009624985978007317</v>
+        <v>1024.267125001643</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2493,33 +2507,35 @@
       <c r="H9" t="b">
         <v>1</v>
       </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>0.007416994776576757</v>
+        <v>1833.740000030957</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0179160269908607</v>
+        <v>1563.576415996067</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2558,33 +2574,35 @@
       <c r="H10" t="b">
         <v>1</v>
       </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>4344.677207991481</v>
+        <v>15255.30504196649</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01504196552559733</v>
+        <v>1373.105834005401</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2623,33 +2641,35 @@
       <c r="H11" t="b">
         <v>1</v>
       </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>0.006457965355366468</v>
+        <v>15064.77179203648</v>
       </c>
       <c r="M11" t="n">
-        <v>0.03062502946704626</v>
+        <v>1064.742916962132</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2688,33 +2708,35 @@
       <c r="H12" t="b">
         <v>1</v>
       </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>0.009875046089291573</v>
+        <v>4114.314374979585</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01654104562476277</v>
+        <v>1277.341959008481</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2753,33 +2775,35 @@
       <c r="H13" t="b">
         <v>1</v>
       </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>0.006167043466120958</v>
+        <v>1864.897291001398</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01658301334828138</v>
+        <v>1248.87975002639</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2818,33 +2842,35 @@
       <c r="H14" t="b">
         <v>1</v>
       </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>14358.48670802079</v>
+        <v>11307.84758296795</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0315410434268415</v>
+        <v>1974.152791954111</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2883,33 +2909,35 @@
       <c r="H15" t="b">
         <v>1</v>
       </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>7356.289791991003</v>
+        <v>8975.631333014462</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01512496965005994</v>
+        <v>1549.375167000107</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2948,33 +2976,35 @@
       <c r="H16" t="b">
         <v>1</v>
       </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>0.006584043148905039</v>
+        <v>10569.15116700111</v>
       </c>
       <c r="M16" t="n">
-        <v>0.01837499439716339</v>
+        <v>1783.380625012796</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -3013,33 +3043,35 @@
       <c r="H17" t="b">
         <v>1</v>
       </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>0.02758397022262216</v>
+        <v>7943.166791985277</v>
       </c>
       <c r="M17" t="n">
-        <v>0.008500006515532732</v>
+        <v>1841.219791036565</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -3078,33 +3110,35 @@
       <c r="H18" t="b">
         <v>1</v>
       </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>0.005375011824071407</v>
+        <v>1981.59337497782</v>
       </c>
       <c r="M18" t="n">
-        <v>0.01204200088977814</v>
+        <v>1919.178374984767</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: kimi Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: kimi transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
